--- a/research/traditional_assets/database/data/jamaica/jamaica_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_brokerage_investment_banking.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.3075</v>
+        <v>0.2929</v>
       </c>
       <c r="E2">
-        <v>0.542</v>
+        <v>0.5489999999999999</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>98.10000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="L2">
-        <v>0.4849233811171528</v>
+        <v>0.4786458333333334</v>
       </c>
       <c r="M2">
-        <v>21.9</v>
+        <v>37.48</v>
       </c>
       <c r="N2">
-        <v>0.01712543009071004</v>
+        <v>0.0299098236373793</v>
       </c>
       <c r="O2">
-        <v>0.2232415902140673</v>
+        <v>0.4078346028291622</v>
       </c>
       <c r="P2">
-        <v>11.4</v>
+        <v>32.55</v>
       </c>
       <c r="Q2">
-        <v>0.0089146074444792</v>
+        <v>0.02597558056021068</v>
       </c>
       <c r="R2">
-        <v>0.1162079510703364</v>
+        <v>0.3541893362350381</v>
       </c>
       <c r="S2">
-        <v>10.5</v>
+        <v>4.93</v>
       </c>
       <c r="T2">
-        <v>0.4794520547945206</v>
+        <v>0.1315368196371398</v>
       </c>
       <c r="U2">
-        <v>471.3</v>
+        <v>437.62</v>
       </c>
       <c r="V2">
-        <v>0.3685486393493901</v>
+        <v>0.3492299098236374</v>
       </c>
       <c r="W2">
-        <v>0.1721234829462231</v>
+        <v>0.1298079992608856</v>
       </c>
       <c r="X2">
-        <v>0.1386693945977004</v>
+        <v>0.2873841645191318</v>
       </c>
       <c r="Y2">
-        <v>0.03345408834852265</v>
+        <v>-0.1575761652582462</v>
       </c>
       <c r="Z2">
-        <v>0.08273250369085935</v>
+        <v>0.06710400771696087</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07291360188788151</v>
+        <v>0.1288323582331551</v>
       </c>
       <c r="AC2">
-        <v>-0.07291360188788151</v>
+        <v>-0.1288323582331551</v>
       </c>
       <c r="AD2">
-        <v>2642.6</v>
+        <v>3182.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2642.6</v>
+        <v>3182.4</v>
       </c>
       <c r="AG2">
-        <v>2171.3</v>
+        <v>2744.78</v>
       </c>
       <c r="AH2">
-        <v>0.6738919773550263</v>
+        <v>0.7174839364220493</v>
       </c>
       <c r="AI2">
-        <v>0.7898024447831675</v>
+        <v>0.8572121212121212</v>
       </c>
       <c r="AJ2">
-        <v>0.6293440769832759</v>
+        <v>0.6865588762043883</v>
       </c>
       <c r="AK2">
-        <v>0.7553398733736868</v>
+        <v>0.8381314735196405</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.48</v>
+        <v>0.502</v>
       </c>
       <c r="E3">
-        <v>0.8129999999999999</v>
+        <v>0.828</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,85 +728,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>27.7</v>
+        <v>27.4</v>
       </c>
       <c r="L3">
-        <v>0.6210762331838565</v>
+        <v>0.5111940298507462</v>
       </c>
       <c r="M3">
-        <v>10.5</v>
+        <v>31.03</v>
       </c>
       <c r="N3">
-        <v>0.01355713363460297</v>
+        <v>0.03810166994106091</v>
       </c>
       <c r="O3">
-        <v>0.3790613718411552</v>
+        <v>1.132481751824818</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>26.1</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.03204813359528488</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.9525547445255476</v>
       </c>
       <c r="S3">
-        <v>10.5</v>
+        <v>4.93</v>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>0.1588785046728972</v>
       </c>
       <c r="U3">
-        <v>26.1</v>
+        <v>6.52</v>
       </c>
       <c r="V3">
-        <v>0.03369916074887024</v>
+        <v>0.008005893909626719</v>
       </c>
       <c r="W3">
-        <v>0.1467161016949153</v>
+        <v>0.1137873754152824</v>
       </c>
       <c r="X3">
-        <v>0.07128524142137277</v>
+        <v>0.1395360916027704</v>
       </c>
       <c r="Y3">
-        <v>0.07543086027354248</v>
+        <v>-0.02574871618748799</v>
       </c>
       <c r="Z3">
-        <v>0.1086665204785225</v>
+        <v>0.0988875154511743</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06582435018580177</v>
+        <v>0.1230906602892633</v>
       </c>
       <c r="AC3">
-        <v>-0.06582435018580177</v>
+        <v>-0.1230906602892633</v>
       </c>
       <c r="AD3">
-        <v>320.5</v>
+        <v>469.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>320.5</v>
+        <v>469.7</v>
       </c>
       <c r="AG3">
-        <v>294.4</v>
+        <v>463.18</v>
       </c>
       <c r="AH3">
-        <v>0.2926940639269406</v>
+        <v>0.3657814811930535</v>
       </c>
       <c r="AI3">
-        <v>0.5640619500175994</v>
+        <v>0.6876006441223832</v>
       </c>
       <c r="AJ3">
-        <v>0.2754233323977921</v>
+        <v>0.3625448112838335</v>
       </c>
       <c r="AK3">
-        <v>0.5430732337207158</v>
+        <v>0.6845901445505336</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.135</v>
+        <v>0.08380000000000001</v>
       </c>
       <c r="E4">
-        <v>0.271</v>
+        <v>0.27</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,28 +850,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>70.40000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="L4">
-        <v>0.446417247939125</v>
+        <v>0.4660404624277457</v>
       </c>
       <c r="M4">
-        <v>11.4</v>
+        <v>6.45</v>
       </c>
       <c r="N4">
-        <v>0.02260559190957763</v>
+        <v>0.01470253020287212</v>
       </c>
       <c r="O4">
-        <v>0.1619318181818182</v>
+        <v>0.1</v>
       </c>
       <c r="P4">
-        <v>11.4</v>
+        <v>6.45</v>
       </c>
       <c r="Q4">
-        <v>0.02260559190957763</v>
+        <v>0.01470253020287212</v>
       </c>
       <c r="R4">
-        <v>0.1619318181818182</v>
+        <v>0.1</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -880,55 +880,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>445.2</v>
+        <v>431.1</v>
       </c>
       <c r="V4">
-        <v>0.8828078524687686</v>
+        <v>0.9826760884431275</v>
       </c>
       <c r="W4">
-        <v>0.1975308641975309</v>
+        <v>0.1458286231064888</v>
       </c>
       <c r="X4">
-        <v>0.2060535477740281</v>
+        <v>0.4352322374354933</v>
       </c>
       <c r="Y4">
-        <v>-0.008522683576497186</v>
+        <v>-0.2894036143290045</v>
       </c>
       <c r="Z4">
-        <v>0.07750147434637311</v>
+        <v>0.05967575025870989</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.08000285358996125</v>
+        <v>0.1345740561770468</v>
       </c>
       <c r="AC4">
-        <v>-0.08000285358996125</v>
+        <v>-0.1345740561770468</v>
       </c>
       <c r="AD4">
-        <v>2322.1</v>
+        <v>2712.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2322.1</v>
+        <v>2712.7</v>
       </c>
       <c r="AG4">
-        <v>1876.9</v>
+        <v>2281.6</v>
       </c>
       <c r="AH4">
-        <v>0.8215751485989243</v>
+        <v>0.860792028939519</v>
       </c>
       <c r="AI4">
-        <v>0.8359794074234079</v>
+        <v>0.8954578464382387</v>
       </c>
       <c r="AJ4">
-        <v>0.7882160255333446</v>
+        <v>0.8387310223137154</v>
       </c>
       <c r="AK4">
-        <v>0.8046730975348338</v>
+        <v>0.8781126120925221</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/research/traditional_assets/database/data/jamaica/jamaica_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_brokerage_investment_banking.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.2929</v>
+        <v>0.2651</v>
       </c>
       <c r="E2">
-        <v>0.5489999999999999</v>
+        <v>0.408</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>91.90000000000001</v>
+        <v>100.1</v>
       </c>
       <c r="L2">
-        <v>0.4786458333333334</v>
+        <v>0.5994011976047905</v>
       </c>
       <c r="M2">
-        <v>37.48</v>
+        <v>20.001</v>
       </c>
       <c r="N2">
-        <v>0.0299098236373793</v>
+        <v>0.02178283598344587</v>
       </c>
       <c r="O2">
-        <v>0.4078346028291622</v>
+        <v>0.1998101898101898</v>
       </c>
       <c r="P2">
-        <v>32.55</v>
+        <v>20.001</v>
       </c>
       <c r="Q2">
-        <v>0.02597558056021068</v>
+        <v>0.02178283598344587</v>
       </c>
       <c r="R2">
-        <v>0.3541893362350381</v>
+        <v>0.1998101898101898</v>
       </c>
       <c r="S2">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.1315368196371398</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>437.62</v>
+        <v>385.6</v>
       </c>
       <c r="V2">
-        <v>0.3492299098236374</v>
+        <v>0.4199520801568285</v>
       </c>
       <c r="W2">
-        <v>0.1298079992608856</v>
+        <v>0.1804499903578245</v>
       </c>
       <c r="X2">
-        <v>0.2873841645191318</v>
+        <v>0.235499121551311</v>
       </c>
       <c r="Y2">
-        <v>-0.1575761652582462</v>
+        <v>-0.05504913119348656</v>
       </c>
       <c r="Z2">
-        <v>0.06710400771696087</v>
+        <v>0.05117017299808189</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1288323582331551</v>
+        <v>0.09988774760316337</v>
       </c>
       <c r="AC2">
-        <v>-0.1288323582331551</v>
+        <v>-0.09988774760316337</v>
       </c>
       <c r="AD2">
-        <v>3182.4</v>
+        <v>3325.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3182.4</v>
+        <v>3325.3</v>
       </c>
       <c r="AG2">
-        <v>2744.78</v>
+        <v>2939.7</v>
       </c>
       <c r="AH2">
-        <v>0.7174839364220493</v>
+        <v>0.7836220101331448</v>
       </c>
       <c r="AI2">
-        <v>0.8572121212121212</v>
+        <v>0.8556467591282196</v>
       </c>
       <c r="AJ2">
-        <v>0.6865588762043883</v>
+        <v>0.7619948676741232</v>
       </c>
       <c r="AK2">
-        <v>0.8381314735196405</v>
+        <v>0.8397463364469964</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.502</v>
+        <v>0.5</v>
       </c>
       <c r="E3">
-        <v>0.828</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,85 +728,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>27.4</v>
+        <v>21.7</v>
       </c>
       <c r="L3">
-        <v>0.5111940298507462</v>
+        <v>0.3974358974358974</v>
       </c>
       <c r="M3">
-        <v>31.03</v>
+        <v>19.5</v>
       </c>
       <c r="N3">
-        <v>0.03810166994106091</v>
+        <v>0.03296703296703297</v>
       </c>
       <c r="O3">
-        <v>1.132481751824818</v>
+        <v>0.8986175115207373</v>
       </c>
       <c r="P3">
-        <v>26.1</v>
+        <v>19.5</v>
       </c>
       <c r="Q3">
-        <v>0.03204813359528488</v>
+        <v>0.03296703296703297</v>
       </c>
       <c r="R3">
-        <v>0.9525547445255476</v>
+        <v>0.8986175115207373</v>
       </c>
       <c r="S3">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.1588785046728972</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>6.52</v>
+        <v>12.4</v>
       </c>
       <c r="V3">
-        <v>0.008005893909626719</v>
+        <v>0.0209636517328825</v>
       </c>
       <c r="W3">
-        <v>0.1137873754152824</v>
+        <v>0.1054421768707483</v>
       </c>
       <c r="X3">
-        <v>0.1395360916027704</v>
+        <v>0.1113390394649978</v>
       </c>
       <c r="Y3">
-        <v>-0.02574871618748799</v>
+        <v>-0.0058968625942495</v>
       </c>
       <c r="Z3">
-        <v>0.0988875154511743</v>
+        <v>0.08087451119800924</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1230906602892633</v>
+        <v>0.09503146000478138</v>
       </c>
       <c r="AC3">
-        <v>-0.1230906602892633</v>
+        <v>-0.09503146000478138</v>
       </c>
       <c r="AD3">
-        <v>469.7</v>
+        <v>532.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>469.7</v>
+        <v>532.7</v>
       </c>
       <c r="AG3">
-        <v>463.18</v>
+        <v>520.3000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.3657814811930535</v>
+        <v>0.4738480697384807</v>
       </c>
       <c r="AI3">
-        <v>0.6876006441223832</v>
+        <v>0.7000919963201472</v>
       </c>
       <c r="AJ3">
-        <v>0.3625448112838335</v>
+        <v>0.4679798524914553</v>
       </c>
       <c r="AK3">
-        <v>0.6845901445505336</v>
+        <v>0.6951235804943221</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.08380000000000001</v>
+        <v>0.0302</v>
       </c>
       <c r="E4">
-        <v>0.27</v>
+        <v>0.255</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,28 +850,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>64.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="L4">
-        <v>0.4660404624277457</v>
+        <v>0.697508896797153</v>
       </c>
       <c r="M4">
-        <v>6.45</v>
+        <v>0.501</v>
       </c>
       <c r="N4">
-        <v>0.01470253020287212</v>
+        <v>0.001533516988062443</v>
       </c>
       <c r="O4">
-        <v>0.1</v>
+        <v>0.006390306122448979</v>
       </c>
       <c r="P4">
-        <v>6.45</v>
+        <v>0.501</v>
       </c>
       <c r="Q4">
-        <v>0.01470253020287212</v>
+        <v>0.001533516988062443</v>
       </c>
       <c r="R4">
-        <v>0.1</v>
+        <v>0.006390306122448979</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -880,55 +880,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>431.1</v>
+        <v>373.2</v>
       </c>
       <c r="V4">
-        <v>0.9826760884431275</v>
+        <v>1.142332415059688</v>
       </c>
       <c r="W4">
-        <v>0.1458286231064888</v>
+        <v>0.2554578038449006</v>
       </c>
       <c r="X4">
-        <v>0.4352322374354933</v>
+        <v>0.3596592036376243</v>
       </c>
       <c r="Y4">
-        <v>-0.2894036143290045</v>
+        <v>-0.1042013997927236</v>
       </c>
       <c r="Z4">
-        <v>0.05967575025870989</v>
+        <v>0.04342283175584315</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.1345740561770468</v>
+        <v>0.1047440352015453</v>
       </c>
       <c r="AC4">
-        <v>-0.1345740561770468</v>
+        <v>-0.1047440352015453</v>
       </c>
       <c r="AD4">
-        <v>2712.7</v>
+        <v>2792.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2712.7</v>
+        <v>2792.6</v>
       </c>
       <c r="AG4">
-        <v>2281.6</v>
+        <v>2419.4</v>
       </c>
       <c r="AH4">
-        <v>0.860792028939519</v>
+        <v>0.8952649632930466</v>
       </c>
       <c r="AI4">
-        <v>0.8954578464382387</v>
+        <v>0.8935176297433928</v>
       </c>
       <c r="AJ4">
-        <v>0.8387310223137154</v>
+        <v>0.8810312807253924</v>
       </c>
       <c r="AK4">
-        <v>0.8781126120925221</v>
+        <v>0.8790785553375481</v>
       </c>
       <c r="AL4">
         <v>0</v>
